--- a/outputs/monitor_xlsx/20260213.xlsx
+++ b/outputs/monitor_xlsx/20260213.xlsx
@@ -473,6 +473,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -536,10 +537,6 @@
           <t>-1.73%</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -562,10 +559,6 @@
           <t>-2.92%</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -588,10 +581,6 @@
           <t>-0.44%</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -614,10 +603,6 @@
           <t>-2.50%</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -640,10 +625,6 @@
           <t>+17.96%</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -661,7 +642,6 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>105.98億</t>
@@ -699,7 +679,6 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>39.16億</t>
@@ -710,8 +689,6 @@
           <t>195.78億</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -729,15 +706,11 @@
           <t>145.98%</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>164.08%</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -755,11 +728,6 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -777,15 +745,11 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>14019口</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -803,7 +767,6 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>24.77億</t>
@@ -853,6 +816,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
@@ -908,10 +872,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-    </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -1033,7 +994,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W18"/>
+  <dimension ref="A1:V18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1068,6 +1029,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -1146,40 +1108,35 @@
       </c>
       <c r="P3" s="5" t="inlineStr">
         <is>
-          <t>籌碼評價</t>
+          <t>買賣券商差</t>
         </is>
       </c>
       <c r="Q3" s="5" t="inlineStr">
         <is>
-          <t>買賣券商差</t>
+          <t>籌碼集中度5D(%)</t>
         </is>
       </c>
       <c r="R3" s="5" t="inlineStr">
         <is>
-          <t>籌碼集中度5D(%)</t>
+          <t>借券賣出餘額</t>
         </is>
       </c>
       <c r="S3" s="5" t="inlineStr">
         <is>
-          <t>借券賣出餘額</t>
+          <t>短回補天數</t>
         </is>
       </c>
       <c r="T3" s="5" t="inlineStr">
         <is>
-          <t>短回補天數</t>
+          <t>VWAP20D</t>
         </is>
       </c>
       <c r="U3" s="5" t="inlineStr">
         <is>
-          <t>VWAP20D</t>
+          <t>VWAP乖離(%)</t>
         </is>
       </c>
       <c r="V3" s="5" t="inlineStr">
-        <is>
-          <t>VWAP乖離(%)</t>
-        </is>
-      </c>
-      <c r="W3" s="5" t="inlineStr">
         <is>
           <t>資料來源</t>
         </is>
@@ -1196,7 +1153,6 @@
           <t>0050</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>-14398</v>
       </c>
@@ -1206,12 +1162,7 @@
       <c r="M4" t="n">
         <v>37522</v>
       </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1228,7 +1179,6 @@
           <t>S&amp;P黃金正2</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
       <c r="H5" t="n">
         <v>1491</v>
       </c>
@@ -1238,12 +1188,7 @@
       <c r="M5" t="n">
         <v>49235</v>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1260,7 +1205,6 @@
           <t>華城</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
       <c r="H6" t="n">
         <v>849</v>
       </c>
@@ -1270,12 +1214,7 @@
       <c r="M6" t="n">
         <v>14376</v>
       </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1292,7 +1231,6 @@
           <t>台達電</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
       <c r="H7" t="n">
         <v>-6530</v>
       </c>
@@ -1302,12 +1240,7 @@
       <c r="M7" t="n">
         <v>30813</v>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1324,7 +1257,6 @@
           <t>台積電</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
       <c r="H8" t="n">
         <v>-5631</v>
       </c>
@@ -1334,12 +1266,7 @@
       <c r="M8" t="n">
         <v>111537</v>
       </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1356,7 +1283,6 @@
           <t>華邦電</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
       <c r="H9" t="n">
         <v>-16542</v>
       </c>
@@ -1366,12 +1292,7 @@
       <c r="M9" t="n">
         <v>698571</v>
       </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1388,7 +1309,6 @@
           <t>台光電</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
       <c r="H10" t="n">
         <v>-2642</v>
       </c>
@@ -1398,12 +1318,7 @@
       <c r="M10" t="n">
         <v>10783</v>
       </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1420,7 +1335,6 @@
           <t>世芯-KY</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
       <c r="H11" t="n">
         <v>-229</v>
       </c>
@@ -1430,12 +1344,7 @@
       <c r="M11" t="n">
         <v>29836</v>
       </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1452,7 +1361,6 @@
           <t>光聖</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
       <c r="H12" t="n">
         <v>517</v>
       </c>
@@ -1462,12 +1370,7 @@
       <c r="M12" t="n">
         <v>21377</v>
       </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1484,7 +1387,6 @@
           <t>聯亞</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
       <c r="H13" t="n">
         <v>319</v>
       </c>
@@ -1494,12 +1396,7 @@
       <c r="M13" t="n">
         <v>-374</v>
       </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>主力積極買進</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1516,7 +1413,6 @@
           <t>威剛</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
       <c r="H14" t="n">
         <v>-4021</v>
       </c>
@@ -1526,12 +1422,7 @@
       <c r="M14" t="n">
         <v>-903</v>
       </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1548,7 +1439,6 @@
           <t>台新科</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
       <c r="H15" t="n">
         <v>-331</v>
       </c>
@@ -1558,12 +1448,7 @@
       <c r="M15" t="n">
         <v>-3</v>
       </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1580,7 +1465,6 @@
           <t>華星光</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
       <c r="H16" t="n">
         <v>-1049</v>
       </c>
@@ -1590,12 +1474,7 @@
       <c r="M16" t="n">
         <v>-1637</v>
       </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1612,7 +1491,6 @@
           <t>景碩</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
       <c r="H17" t="n">
         <v>-8238</v>
       </c>
@@ -1622,12 +1500,7 @@
       <c r="M17" t="n">
         <v>105442</v>
       </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1644,7 +1517,6 @@
           <t>耀登</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
       <c r="H18" t="n">
         <v>-314</v>
       </c>
@@ -1654,12 +1526,7 @@
       <c r="M18" t="n">
         <v>20437</v>
       </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
